--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/01_business_functions.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/01_business_functions.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Red1494f9634341b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Raf17d77e0b2b4cfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R99ae73861b274ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R0a38a15152f14b00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R162d6c3f74214ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R3047d88732474636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rb86e36a8b7ca4866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R61b13e74d8a34c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rb0b502d12b1b4ce7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rb0f71b397e684c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R7b42e61ec9b74de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R6fe11ed7c5ff45bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,7 +624,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85cb6ffe4054478c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re03540d26a3f4d77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -785,7 +785,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M6" s="80" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Executive Office (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for business functions.</x:v>
       </x:c>
       <x:c r="N6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -829,7 +829,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M7" s="81" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm Provider Operations (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this business functions record is used downstream.</x:v>
       </x:c>
       <x:c r="N7" s="43" t="str">
         <x:v>High</x:v>
@@ -873,7 +873,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M8" s="82" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Attach client evidence for Claims Operations (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N8" s="45" t="str">
         <x:v>High</x:v>
@@ -917,7 +917,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Reconcile Eligibility and Benefits (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N9" t="str">
         <x:v>High</x:v>
@@ -961,7 +961,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N10" t="str">
         <x:v>High</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M11" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Contact Center and Member Service (record 6) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N11" t="str">
         <x:v>Medium</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm Revenue Cycle Operations (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this business functions record is used downstream.</x:v>
       </x:c>
       <x:c r="N12" t="str">
         <x:v>High</x:v>
@@ -1093,7 +1093,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M13" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Finance Analytics (record 8) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N13" t="str">
         <x:v>High</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Reconcile Workforce Analytics (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N14" t="str">
         <x:v>High</x:v>
@@ -1181,7 +1181,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M15" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N15" t="str">
         <x:v>High</x:v>
@@ -1225,7 +1225,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Claims and Payment Analytics (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for business functions.</x:v>
       </x:c>
       <x:c r="N16" t="str">
         <x:v>Medium</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm Provider Performance Analytics (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this business functions record is used downstream.</x:v>
       </x:c>
       <x:c r="N17" t="str">
         <x:v>High</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Attach client evidence for Enterprise Data Platform (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N18" t="str">
         <x:v>High</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Reconcile Data Governance and Data Quality (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N19" t="str">
         <x:v>High</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M20" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action (record 15) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N20" t="str">
         <x:v>High</x:v>
@@ -1445,7 +1445,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for business functions.</x:v>
       </x:c>
       <x:c r="N21" t="str">
         <x:v>Medium</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M22" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this business functions record is used downstream.</x:v>
       </x:c>
       <x:c r="N22" t="str">
         <x:v>High</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N23" t="str">
         <x:v>High</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Reconcile Infrastructure and CMDB (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N24" t="str">
         <x:v>High</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N25" t="str">
         <x:v>High</x:v>
@@ -1648,7 +1648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re005cd70a874483e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab6e99aa42ba47b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1778,7 +1778,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd147a22254394f24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2d8836b01b348aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22b369496e2747ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabba6668c17a4871"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2074,7 +2074,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf3713782d2a4e4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85d2254a84384455"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2184,7 +2184,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93b13abfa80241b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e0789d5c2284683"/>
   </x:tableParts>
 </x:worksheet>
 </file>